--- a/artfynd/A 23669-2020 artfynd.xlsx
+++ b/artfynd/A 23669-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23669-2020 artfynd.xlsx
+++ b/artfynd/A 23669-2020 artfynd.xlsx
@@ -6172,7 +6172,7 @@
         <v>104147206</v>
       </c>
       <c r="B47" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623202.4779175948</v>
+        <v>623203</v>
       </c>
       <c r="R47" t="n">
-        <v>6951835.838492052</v>
+        <v>6951836</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6247,19 +6247,9 @@
           <t>2022-09-10</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-09-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">

--- a/artfynd/A 23669-2020 artfynd.xlsx
+++ b/artfynd/A 23669-2020 artfynd.xlsx
@@ -6172,7 +6172,7 @@
         <v>104147206</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 23669-2020 artfynd.xlsx
+++ b/artfynd/A 23669-2020 artfynd.xlsx
@@ -6172,7 +6172,7 @@
         <v>104147206</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 23669-2020 artfynd.xlsx
+++ b/artfynd/A 23669-2020 artfynd.xlsx
@@ -6172,7 +6172,7 @@
         <v>104147206</v>
       </c>
       <c r="B47" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
